--- a/collateral/SimReal-资源与渠道清单.xlsx
+++ b/collateral/SimReal-资源与渠道清单.xlsx
@@ -3845,11 +3845,7 @@
           <t>已截止</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2027-02-05</t>
-        </is>
-      </c>
+      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>项目期 2026-09-14 至 2027-02-05；申请已于 5/3 截止；下一期未确认</t>
@@ -5892,7 +5888,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>AWS Generative AI Accelerator</t>
+          <t>Sequoia Arc</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -5902,7 +5898,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>全球</t>
+          <t>仅限总部在美洲或欧洲的公司（中国总部不符合）</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -5910,29 +5906,25 @@
           <t>已截止</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>2027-07-10</t>
-        </is>
-      </c>
+      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2026 期申请窗口为 6/10–7/10，已截止。2025、2026 两期都在年中开放；2027 期的具体时间未确认。</t>
+          <t>已截止；Fall 2026 截止为 2026-08-17；每年两次公开申请，下一期时间未确认</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>最高 $1,000,000 AWS 促销额度，8 周导师辅导，免费参加 AWS re:Invent；不占股，不收费。形式为混合制：西雅图线下启动，6 周线上，最后在拉斯维加斯 re:Invent 收官。</t>
+          <t>$500K–$1M（条款按公司定制）；7 周 Company Building Immersion，含 Sequoia 合伙人、客户对接与投资人网络</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>做生成式或 agentic AI 的早期创业公司；每期选约 40 家 late-seed 至 Series A 的公司。</t>
+          <t>pre-seed 或 seed 阶段创始人；公司总部须位于美洲或欧洲</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>额度极大，且在 re:Invent 收官，能接触 AWS 生态里的 AI 公司（潜在买家）。但该项目偏 late-seed 以上，SimReal 完成 $20M 种子轮后申请 2027 期更有竞争力。</t>
+          <t>Sequoia 品牌和客户对接直接服务 $20M 种子轮与 AI 公司客户拓展；需先确定英国或美国实体</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -5942,152 +5934,152 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>在 aws.amazon.com/startups/programs/generative-ai 关注 2027 期开放。</t>
+          <t>sequoiacap.com/arc 公开申请；另有被 Sequoia 主动发掘（sourced）的推荐路径</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>https://startupintros.com/resources/sequoia-arc-fall-2026
+https://hub.causo.ai/guides/how-to-apply-to-sequoia-arc-2026
+https://sequoiacap.com/arc</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>未复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Accelerate Cambridge (Cambridge Judge Business School)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>加速器与孵化器</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>英国剑桥</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>已截止</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Autumn 2026 期 2026-09-24 至 12-03，申请截止 2026-05-29，已截止；下一期未确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Judge 商学院加速器项目（资金条款本次来源未确认）</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>团队至少 2 人，至少一位创始人有剑桥关联（在校生、校友、教职员工或剑桥镇居民），团队成员学期内需在剑桥</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>创始人剑桥背景符合关联要求，申请成本低；但要求团队学期内驻剑桥</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>低</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>上传 60 秒 pitch 视频到 YouTube/Vimeo，把链接发到 accelerate@jbs.cam.ac.uk</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.jbs.cam.ac.uk/entrepreneurship/programmes/accelerate-cambridge/programmes/apply/</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>未复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>AWS Generative AI Accelerator</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>加速器与孵化器</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>全球</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>已截止</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2026 期申请窗口为 6/10–7/10，已截止。2025、2026 两期都在年中开放；2027 期的具体时间未确认。</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>最高 $1,000,000 AWS 促销额度，8 周导师辅导，免费参加 AWS re:Invent；不占股，不收费。形式为混合制：西雅图线下启动，6 周线上，最后在拉斯维加斯 re:Invent 收官。</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>做生成式或 agentic AI 的早期创业公司；每期选约 40 家 late-seed 至 Series A 的公司。</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>额度极大，且在 re:Invent 收官，能接触 AWS 生态里的 AI 公司（潜在买家）。但该项目偏 late-seed 以上，SimReal 完成 $20M 种子轮后申请 2027 期更有竞争力。</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>在 aws.amazon.com/startups/programs/generative-ai 关注 2027 期开放。</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>https://aws.amazon.com/startups/programs/generative-ai
 https://grantedai.com/grants/aws-generative-ai-accelerator-ai-startups-aws-e7f8a9b0
 https://startupintros.com/resources/aws-generative-ai-accelerator-2026
 https://aws.amazon.com/aws-startups/learn/aws-announces-21-startups-selected-for-the-aws-generative-ai-accelerator/</t>
-        </is>
-      </c>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>未复核</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Sequoia Arc</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>加速器与孵化器</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>仅限总部在美洲或欧洲的公司（中国总部不符合）</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>已截止</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr"/>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>已截止；Fall 2026 截止为 2026-08-17；每年两次公开申请，下一期时间未确认</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>$500K–$1M（条款按公司定制）；7 周 Company Building Immersion，含 Sequoia 合伙人、客户对接与投资人网络</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>pre-seed 或 seed 阶段创始人；公司总部须位于美洲或欧洲</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Sequoia 品牌和客户对接直接服务 $20M 种子轮与 AI 公司客户拓展；需先确定英国或美国实体</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>sequoiacap.com/arc 公开申请；另有被 Sequoia 主动发掘（sourced）的推荐路径</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>https://startupintros.com/resources/sequoia-arc-fall-2026
-https://hub.causo.ai/guides/how-to-apply-to-sequoia-arc-2026
-https://sequoiacap.com/arc</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>未复核</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Accelerate Cambridge (Cambridge Judge Business School)</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>加速器与孵化器</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>英国剑桥</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>已截止</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr"/>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>Autumn 2026 期 2026-09-24 至 12-03，申请截止 2026-05-29，已截止；下一期未确认</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Judge 商学院加速器项目（资金条款本次来源未确认）</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>团队至少 2 人，至少一位创始人有剑桥关联（在校生、校友、教职员工或剑桥镇居民），团队成员学期内需在剑桥</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>创始人剑桥背景符合关联要求，申请成本低；但要求团队学期内驻剑桥</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>低</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>上传 60 秒 pitch 视频到 YouTube/Vimeo，把链接发到 accelerate@jbs.cam.ac.uk</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>https://www.jbs.cam.ac.uk/entrepreneurship/programmes/accelerate-cambridge/programmes/apply/</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -11295,280 +11287,272 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
+          <t>OpenEnv Hackathon SF (PyTorch x Cerebral Valley x Shack15)</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>比赛与奖金</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>美国旧金山</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>已截止</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-07 至 03-08 已举办；下一届未确认</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>参赛者构建 RL 环境并对 base model 做后训练以提升基准表现；5 个主题（RL 与 agentic orchestration）；现金奖池 $100K+</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>报名参赛，具体条件未确认</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="inlineStr">
+        <is>
+          <t>与 SimReal 的产品（RL 环境 + 后训练）完全重合，是展示金融环境、结识 Meta/PyTorch 团队和 RL 开发者的理想场景</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>关注 pytorch.org 活动页和 cerebralvalley.ai；下一届可争取赛题/环境提供方或评委角色，或按 OpenEnv 规范开源一个精简版金融环境</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr"/>
+      <c r="N113" s="2" t="inlineStr">
+        <is>
+          <t>https://cerebralvalley.ai/e/openenv-hackathon-sf
+https://pytorch.org/event/openenv-hackathon-sf/</t>
+        </is>
+      </c>
+      <c r="O113" s="2" t="inlineStr">
+        <is>
+          <t>未复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>TechCrunch Startup Battlefield 200</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>比赛与奖金</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>全球（2026 届覆盖各行业和地区）</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>已截止</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr"/>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>已截止；2026 届申请 5/27 截止并延至 6/8，8 月底通知；2027 届日期未确认</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>入选的 200 家早期公司在 Disrupt 现场展示，面向 10,000+ 观众、顶级 VC 和全球媒体</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>早期创业公司；具体条件未确认</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="inlineStr">
+        <is>
+          <t>媒体曝光和投资人背书强，但对 B2B 数据/RL 基础设施的买家价值有限</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>参考 techcrunch.com/startup-battlefield/about 和 TC 发布的“我们在找什么”文章，2027 年春季提前准备</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr"/>
+      <c r="N114" s="2" t="inlineStr">
+        <is>
+          <t>https://techcrunch.com/startup-battlefield/about/
+https://techcrunch.com/2026/05/28/how-to-apply-to-startup-battlefield-2026-what-you-need-ahead-of-the-june-8-deadline/
+https://techcrunch.com/2026/08/20/the-2026-startup-battlefield-200-is-here-see-who-made-the-cut/
+https://techcrunch.com/2026/05/26/what-were-looking-for-in-startup-battlefield-2026-and-how-to-apply-in-time-for-the-may-27-deadline/</t>
+        </is>
+      </c>
+      <c r="O114" s="2" t="inlineStr">
+        <is>
+          <t>未复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>2026数字中国创新大赛·人工智能赛道</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>比赛与奖金</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>中国大陆</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>已截止</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr"/>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>报名和作品提交在2月27日至3月31日，4月初初审、4月11–12日复赛、4月下旬决赛；已截止，下一届时间未确认。</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>数字中国建设峰会官方赛事的AI赛道（奖金未确认）。</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>未确认</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="inlineStr">
+        <is>
+          <t>本届已结束，作为2027年的备选。</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>关注数字中国建设峰会官网的下一届通知。</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr"/>
+      <c r="N115" s="2" t="inlineStr">
+        <is>
+          <t>https://www.szzg.gov.cn/2025/xwzx/fhzx/202603/t20260306_5292292.htm
+https://www.szzg.gov.cn/2025/xwzx/fhzx/202603/t20260317_5296624.htm</t>
+        </is>
+      </c>
+      <c r="O115" s="2" t="inlineStr">
+        <is>
+          <t>未复核</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>Meta PyTorch OpenEnv AI Hackathon（印度）</t>
         </is>
       </c>
-      <c r="C113" s="2" t="inlineStr">
+      <c r="C116" s="2" t="inlineStr">
         <is>
           <t>比赛与奖金</t>
         </is>
       </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>印度（线上初赛 + 班加罗尔线下决赛）</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>已截止</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
-        <is>
-          <t>2027-04-08</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr"/>
+      <c r="G116" s="2" t="inlineStr">
         <is>
           <t>2026-03-14 至 2026-04-26（线上第一轮 3/25–4/8，班加罗尔决赛 4/25–26）</t>
         </is>
       </c>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>$30,000 奖金池，Meta 和 Hugging Face AI 团队的直接面试机会，Meta 官方证书。</t>
         </is>
       </c>
-      <c r="I113" s="2" t="inlineStr">
+      <c r="I116" s="2" t="inlineStr">
         <is>
           <t>1–3 人团队，不要求 RL 经验；面向印度开发者（更细的地区限制未确认）。</t>
         </is>
       </c>
-      <c r="J113" s="2" t="inlineStr">
+      <c r="J116" s="2" t="inlineStr">
         <is>
           <t>面向个人开发者，偏招聘性质。对 SimReal 的价值主要是一个信号：Meta/HF 在投入环境生态，以后可能有面向公司的环境挑战。</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr">
+      <c r="K116" s="2" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="L113" s="2" t="inlineStr">
+      <c r="L116" s="2" t="inlineStr">
         <is>
           <t>已截止；下一期或全球版时间未确认，可以关注 PyTorch 和 Hugging Face 的 X 账号。</t>
         </is>
       </c>
-      <c r="M113" s="2" t="inlineStr">
+      <c r="M116" s="2" t="inlineStr">
         <is>
           <t>AVB 在 X 上称“Meta、Hugging Face 和 PyTorch 这三巨头在办 RL 黑客松”。https://x.com/neural_avb/status/2036484526399160615</t>
         </is>
       </c>
-      <c r="N113" s="2" t="inlineStr">
+      <c r="N116" s="2" t="inlineStr">
         <is>
           <t>https://pytorch.org/event/openenv-ai-hackathon/
 https://x.com/PyTorch/status/2036276566372598162
 https://x.com/neural_avb/status/2036484526399160615
 https://kalinga.ai/openenv-ai-hackathon-india-2026/</t>
-        </is>
-      </c>
-      <c r="O113" s="2" t="inlineStr">
-        <is>
-          <t>未复核</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="2" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>TechCrunch Startup Battlefield 200</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>比赛与奖金</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
-        <is>
-          <t>全球（2026 届覆盖各行业和地区）</t>
-        </is>
-      </c>
-      <c r="E114" s="2" t="inlineStr">
-        <is>
-          <t>已截止</t>
-        </is>
-      </c>
-      <c r="F114" s="2" t="inlineStr">
-        <is>
-          <t>2027-05-27</t>
-        </is>
-      </c>
-      <c r="G114" s="2" t="inlineStr">
-        <is>
-          <t>已截止；2026 届申请 5/27 截止并延至 6/8，8 月底通知；2027 届日期未确认</t>
-        </is>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>入选的 200 家早期公司在 Disrupt 现场展示，面向 10,000+ 观众、顶级 VC 和全球媒体</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>早期创业公司；具体条件未确认</t>
-        </is>
-      </c>
-      <c r="J114" s="2" t="inlineStr">
-        <is>
-          <t>媒体曝光和投资人背书强，但对 B2B 数据/RL 基础设施的买家价值有限</t>
-        </is>
-      </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="L114" s="2" t="inlineStr">
-        <is>
-          <t>参考 techcrunch.com/startup-battlefield/about 和 TC 发布的“我们在找什么”文章，2027 年春季提前准备</t>
-        </is>
-      </c>
-      <c r="M114" s="2" t="inlineStr"/>
-      <c r="N114" s="2" t="inlineStr">
-        <is>
-          <t>https://techcrunch.com/startup-battlefield/about/
-https://techcrunch.com/2026/05/28/how-to-apply-to-startup-battlefield-2026-what-you-need-ahead-of-the-june-8-deadline/
-https://techcrunch.com/2026/08/20/the-2026-startup-battlefield-200-is-here-see-who-made-the-cut/
-https://techcrunch.com/2026/05/26/what-were-looking-for-in-startup-battlefield-2026-and-how-to-apply-in-time-for-the-may-27-deadline/</t>
-        </is>
-      </c>
-      <c r="O114" s="2" t="inlineStr">
-        <is>
-          <t>未复核</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>OpenEnv Hackathon SF (PyTorch x Cerebral Valley x Shack15)</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>比赛与奖金</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
-        <is>
-          <t>美国旧金山</t>
-        </is>
-      </c>
-      <c r="E115" s="2" t="inlineStr">
-        <is>
-          <t>已截止</t>
-        </is>
-      </c>
-      <c r="F115" s="2" t="inlineStr"/>
-      <c r="G115" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-07 至 03-08 已举办；下一届未确认</t>
-        </is>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>参赛者构建 RL 环境并对 base model 做后训练以提升基准表现；5 个主题（RL 与 agentic orchestration）；现金奖池 $100K+</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>报名参赛，具体条件未确认</t>
-        </is>
-      </c>
-      <c r="J115" s="2" t="inlineStr">
-        <is>
-          <t>与 SimReal 的产品（RL 环境 + 后训练）完全重合，是展示金融环境、结识 Meta/PyTorch 团队和 RL 开发者的理想场景</t>
-        </is>
-      </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="L115" s="2" t="inlineStr">
-        <is>
-          <t>关注 pytorch.org 活动页和 cerebralvalley.ai；下一届可争取赛题/环境提供方或评委角色，或按 OpenEnv 规范开源一个精简版金融环境</t>
-        </is>
-      </c>
-      <c r="M115" s="2" t="inlineStr"/>
-      <c r="N115" s="2" t="inlineStr">
-        <is>
-          <t>https://cerebralvalley.ai/e/openenv-hackathon-sf
-https://pytorch.org/event/openenv-hackathon-sf/</t>
-        </is>
-      </c>
-      <c r="O115" s="2" t="inlineStr">
-        <is>
-          <t>未复核</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="n">
-        <v>115</v>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>2026数字中国创新大赛·人工智能赛道</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>比赛与奖金</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
-        <is>
-          <t>中国大陆</t>
-        </is>
-      </c>
-      <c r="E116" s="2" t="inlineStr">
-        <is>
-          <t>已截止</t>
-        </is>
-      </c>
-      <c r="F116" s="2" t="inlineStr"/>
-      <c r="G116" s="2" t="inlineStr">
-        <is>
-          <t>报名和作品提交在2月27日至3月31日，4月初初审、4月11–12日复赛、4月下旬决赛；已截止，下一届时间未确认。</t>
-        </is>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>数字中国建设峰会官方赛事的AI赛道（奖金未确认）。</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>未确认</t>
-        </is>
-      </c>
-      <c r="J116" s="2" t="inlineStr">
-        <is>
-          <t>本届已结束，作为2027年的备选。</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>中</t>
-        </is>
-      </c>
-      <c r="L116" s="2" t="inlineStr">
-        <is>
-          <t>关注数字中国建设峰会官网的下一届通知。</t>
-        </is>
-      </c>
-      <c r="M116" s="2" t="inlineStr"/>
-      <c r="N116" s="2" t="inlineStr">
-        <is>
-          <t>https://www.szzg.gov.cn/2025/xwzx/fhzx/202603/t20260306_5292292.htm
-https://www.szzg.gov.cn/2025/xwzx/fhzx/202603/t20260317_5296624.htm</t>
         </is>
       </c>
       <c r="O116" s="2" t="inlineStr">
